--- a/Analysis/exports/screener_master.xlsx
+++ b/Analysis/exports/screener_master.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026-09-07" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026-09-08" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026-09-07" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,6 +547,3318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:W45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PROBABLE UPSIDE</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Vol Ratio</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Net Accum</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>At Support</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Rising Lows</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Entry Trigger</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Full Trend</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Score /10</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Grasim Industries</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>3297.6</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Sweet Spot</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GRASIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1684.6</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Sweet Spot</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>PB Fintech</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1821</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Sweet Spot</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLICYBZR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>IDFC First Bank</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Sweet Spot</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>GAIL India</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>174.75</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Sweet Spot</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Bank of Maharashtra</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>85.47</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Sweet Spot</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MAHABANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Divi's Laboratories</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9516.5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>596</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HINDZINC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Nykaa</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Kalyan Jewellers</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>610.45</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>CG Power</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>911.4</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CGPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1404.6</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Coforge</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1924.7</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:COFORGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Vodafone Idea</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IDEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4940</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>SUPPORT ENTRY</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="n"/>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n"/>
+      <c r="W20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Support (₹)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Support Type</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Gap %</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Pullback %</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Base Range %</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Prior Trend</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Confluence</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Vol Quiet</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Vol Surge</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Lows Stable</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Reversal</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>Entry Trigger</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>Buy Zone</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>Target (₹)</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>Stop (₹)</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>R:R</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>Score /10</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Delhivery</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>456.05</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>452.5</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>SMA 20</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>₹447.98–461.55</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>524</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>438.93</v>
+      </c>
+      <c r="U22" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V22" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>National Aluminium</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>366.6</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>SMA 200</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>₹362.93–373.93</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="n">
+        <v>421.13</v>
+      </c>
+      <c r="T23" s="7" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="U23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Mazagon Dock</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2470.7</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2460.42</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>SMA 200</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>₹2435.82–2509.63</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>2668.36</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>2386.61</v>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MAZDOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>596</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>589.3200000000001</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>SMA 20</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>₹583.42–601.1</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="n">
+        <v>643.6799999999999</v>
+      </c>
+      <c r="T25" s="7" t="n">
+        <v>571.64</v>
+      </c>
+      <c r="U25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HINDZINC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Premier Energies</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>987.3</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>977.4</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Swing Low</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>₹967.63–996.95</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>1134</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>948.08</v>
+      </c>
+      <c r="U26" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V26" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PREMIERENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix Mills</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>1899</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>1877.3</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Swing Low</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>₹1858.53–1914.85</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="n">
+        <v>2169.8</v>
+      </c>
+      <c r="T27" s="7" t="n">
+        <v>1820.98</v>
+      </c>
+      <c r="U27" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Nestle India</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1408.4</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1405.1</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Swing Low</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>₹1391.05–1433.2</t>
+        </is>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>1553</v>
+      </c>
+      <c r="T28" s="5" t="n">
+        <v>1362.95</v>
+      </c>
+      <c r="U28" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V28" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Hindalco Industries</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>1013</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>1013</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Swing Low</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr">
+        <is>
+          <t>₹1002.87–1033.26</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="n">
+        <v>1094.04</v>
+      </c>
+      <c r="T29" s="7" t="n">
+        <v>982.61</v>
+      </c>
+      <c r="U29" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V29" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HINDALCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>ABB India</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>7398</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>7391.5</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>SMA 50</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>₹7317.59–7539.33</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>7989.84</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>7169.76</v>
+      </c>
+      <c r="U30" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V30" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Nippon India AMC</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>1187</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>1185.87</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>SMA 50</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R31" s="7" t="inlineStr">
+        <is>
+          <t>₹1174.01–1209.59</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="n">
+        <v>1281.96</v>
+      </c>
+      <c r="T31" s="7" t="n">
+        <v>1150.29</v>
+      </c>
+      <c r="U31" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V31" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NAM-INDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Adani Enterprises</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>2954.6</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>2932.8</v>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Swing Low</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>₹2903.47–2991.46</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>3245</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>2844.82</v>
+      </c>
+      <c r="U32" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V32" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Container Corp</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>503.25</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>501.45</v>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>SMA 50</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R33" s="7" t="inlineStr">
+        <is>
+          <t>₹496.44–511.48</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>543.7</v>
+      </c>
+      <c r="T33" s="7" t="n">
+        <v>486.41</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V33" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CONCOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>TVS Motor</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Automobile</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>4108.7</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>4075.1</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>SMA 50</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>₹4034.35–4156.6</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>4484.5</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>3952.84</v>
+      </c>
+      <c r="U34" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V34" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Cochin Shipyard</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1526.5</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>1509.41</v>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>SMA 200</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R35" s="7" t="inlineStr">
+        <is>
+          <t>₹1494.31–1539.6</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="n">
+        <v>1648.62</v>
+      </c>
+      <c r="T35" s="7" t="n">
+        <v>1464.13</v>
+      </c>
+      <c r="U35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:COCHINSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>1376.42</v>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>SMA 50</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>₹1362.65–1403.94</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>1512</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>1335.12</v>
+      </c>
+      <c r="U36" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CDSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>CONSOLIDATION BREAKOUT</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n"/>
+      <c r="U39" s="2" t="n"/>
+      <c r="V39" s="2" t="n"/>
+      <c r="W39" s="3" t="n"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Breakout ₹</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>To Breakout%</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Target ₹</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Stop ₹</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Risk %</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Days Consol.</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>10D Range %</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>BB Width %</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>Vol Ratio</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>SMA Flat</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>Prior Move</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>Vol Pattern</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>Near Breakout</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>BB Squeeze</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>Above SMA200</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>Prior Trend</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>Score /10</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>8828</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>9084.67</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>9748.9</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>8207.75</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V41" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Siemens India</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>3970.9</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>4170.15</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>4429.55</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>3777.51</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="L42" s="7" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N42" s="7" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R42" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T42" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U42" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V42" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W42" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SIEMENS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Eternal (Zomato)</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>321.5</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>334.61</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>353.01</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>306.35</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V43" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ETERNAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>ABB India</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>7398</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>7864.12</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>8316.120000000001</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>7112.84</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R44" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T44" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U44" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V44" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="W44" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Union Bank</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>183.34</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>193.29</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>202.41</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>176.28</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V45" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="W45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A20:W20"/>
+    <mergeCell ref="A39:W39"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1626,8 +4939,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
@@ -3229,8 +6540,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
